--- a/Formato Planilla de Transporte.xlsx
+++ b/Formato Planilla de Transporte.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USUARIO\OneDrive\Documentos\VS code\Agente_Traslados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A562A85-3F02-44B3-9245-3E708C6EFB94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44F6DC6C-89F3-4B0B-9402-96B776E9BA78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FORMATO (2)" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,23 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'FORMATO (2)'!$A$1:$H$32</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -27,9 +43,6 @@
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="10">
   <si>
     <t/>
-  </si>
-  <si>
-    <t>RELACION DE TRASLADOS JULIO</t>
   </si>
   <si>
     <t>FECHA</t>
@@ -54,6 +67,9 @@
   </si>
   <si>
     <t>SubTotal:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RELACION DE TRASLADOS </t>
   </si>
 </sst>
 </file>
@@ -265,9 +281,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -305,7 +321,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -411,7 +427,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -553,7 +569,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -583,7 +599,7 @@
     </row>
     <row r="3" spans="2:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" s="9" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C3" s="10"/>
       <c r="D3" s="10"/>
@@ -593,29 +609,29 @@
     </row>
     <row r="4" spans="2:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="15" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C4" s="16"/>
       <c r="D4" s="17"/>
       <c r="E4" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="F4" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="12" t="s">
+      <c r="G4" s="14" t="s">
         <v>4</v>
-      </c>
-      <c r="G4" s="14" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="5" spans="2:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="D5" s="7" t="s">
         <v>7</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>8</v>
       </c>
       <c r="E5" s="13"/>
       <c r="F5" s="13"/>
@@ -823,7 +839,7 @@
     </row>
     <row r="31" spans="2:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F31" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G31" s="3">
         <f>SUM(G6:G30)</f>
@@ -867,7 +883,7 @@
     </row>
     <row r="3" spans="2:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" s="9" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C3" s="10"/>
       <c r="D3" s="10"/>
@@ -877,29 +893,29 @@
     </row>
     <row r="4" spans="2:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="15" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C4" s="16"/>
       <c r="D4" s="17"/>
       <c r="E4" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="F4" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="12" t="s">
+      <c r="G4" s="14" t="s">
         <v>4</v>
-      </c>
-      <c r="G4" s="14" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="5" spans="2:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="D5" s="7" t="s">
         <v>7</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>8</v>
       </c>
       <c r="E5" s="13"/>
       <c r="F5" s="13"/>
@@ -1107,7 +1123,7 @@
     </row>
     <row r="31" spans="2:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F31" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G31" s="3">
         <f>SUM(G6:G30)</f>

--- a/Formato Planilla de Transporte.xlsx
+++ b/Formato Planilla de Transporte.xlsx
@@ -8,13 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USUARIO\OneDrive\Documentos\VS code\Agente_Traslados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44F6DC6C-89F3-4B0B-9402-96B776E9BA78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6666D274-BDB7-470B-96E9-51BD5F5C3C61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FORMATO (2)" sheetId="1" r:id="rId1"/>
-    <sheet name="AGOSTO 2026" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'FORMATO (2)'!$A$1:$H$32</definedName>
@@ -40,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t/>
   </si>
@@ -857,288 +856,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="78" orientation="landscape" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="B1:G31"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
-    <col min="2" max="2" width="4.44140625" customWidth="1"/>
-    <col min="3" max="3" width="5.109375" customWidth="1"/>
-    <col min="4" max="4" width="5.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="55.44140625" customWidth="1"/>
-    <col min="6" max="6" width="57.5546875" customWidth="1"/>
-    <col min="7" max="7" width="10.6640625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="2:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="10"/>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="10"/>
-      <c r="G3" s="11"/>
-    </row>
-    <row r="4" spans="2:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="C4" s="16"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="12" t="s">
-        <v>2</v>
-      </c>
-      <c r="F4" s="12" t="s">
-        <v>3</v>
-      </c>
-      <c r="G4" s="14" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="2:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E5" s="13"/>
-      <c r="F5" s="13"/>
-      <c r="G5" s="13"/>
-    </row>
-    <row r="6" spans="2:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="5"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="6"/>
-      <c r="G6" s="1"/>
-    </row>
-    <row r="7" spans="2:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="5"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="6"/>
-      <c r="G7" s="1"/>
-    </row>
-    <row r="8" spans="2:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="5"/>
-      <c r="C8" s="8"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="6"/>
-      <c r="G8" s="1"/>
-    </row>
-    <row r="9" spans="2:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="5"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="6"/>
-      <c r="G9" s="1"/>
-    </row>
-    <row r="10" spans="2:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="5"/>
-      <c r="C10" s="8"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="6"/>
-      <c r="G10" s="1"/>
-    </row>
-    <row r="11" spans="2:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="5"/>
-      <c r="C11" s="8"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="6"/>
-      <c r="G11" s="1"/>
-    </row>
-    <row r="12" spans="2:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="5"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="6"/>
-      <c r="G12" s="1"/>
-    </row>
-    <row r="13" spans="2:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="5"/>
-      <c r="C13" s="8"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="6"/>
-      <c r="G13" s="1"/>
-    </row>
-    <row r="14" spans="2:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="5"/>
-      <c r="C14" s="8"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="6"/>
-      <c r="G14" s="1"/>
-    </row>
-    <row r="15" spans="2:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="5"/>
-      <c r="C15" s="8"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="6"/>
-      <c r="G15" s="1"/>
-    </row>
-    <row r="16" spans="2:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="5"/>
-      <c r="C16" s="8"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="6"/>
-      <c r="G16" s="1"/>
-    </row>
-    <row r="17" spans="2:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="5"/>
-      <c r="C17" s="8"/>
-      <c r="D17" s="4"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="6"/>
-      <c r="G17" s="1"/>
-    </row>
-    <row r="18" spans="2:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="5"/>
-      <c r="C18" s="8"/>
-      <c r="D18" s="4"/>
-      <c r="E18" s="5"/>
-      <c r="F18" s="6"/>
-      <c r="G18" s="1"/>
-    </row>
-    <row r="19" spans="2:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="5"/>
-      <c r="C19" s="8"/>
-      <c r="D19" s="4"/>
-      <c r="E19" s="5"/>
-      <c r="F19" s="6"/>
-      <c r="G19" s="1"/>
-    </row>
-    <row r="20" spans="2:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="5"/>
-      <c r="C20" s="8"/>
-      <c r="D20" s="4"/>
-      <c r="E20" s="5"/>
-      <c r="F20" s="6"/>
-      <c r="G20" s="1"/>
-    </row>
-    <row r="21" spans="2:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="5"/>
-      <c r="C21" s="8"/>
-      <c r="D21" s="4"/>
-      <c r="E21" s="5"/>
-      <c r="F21" s="6"/>
-      <c r="G21" s="1"/>
-    </row>
-    <row r="22" spans="2:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="5"/>
-      <c r="C22" s="8"/>
-      <c r="D22" s="4"/>
-      <c r="E22" s="5"/>
-      <c r="F22" s="6"/>
-      <c r="G22" s="1"/>
-    </row>
-    <row r="23" spans="2:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="5"/>
-      <c r="C23" s="8"/>
-      <c r="D23" s="4"/>
-      <c r="E23" s="5"/>
-      <c r="F23" s="6"/>
-      <c r="G23" s="1"/>
-    </row>
-    <row r="24" spans="2:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="5"/>
-      <c r="C24" s="8"/>
-      <c r="D24" s="4"/>
-      <c r="E24" s="5"/>
-      <c r="F24" s="6"/>
-      <c r="G24" s="1"/>
-    </row>
-    <row r="25" spans="2:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="5"/>
-      <c r="C25" s="8"/>
-      <c r="D25" s="4"/>
-      <c r="E25" s="5"/>
-      <c r="F25" s="6"/>
-      <c r="G25" s="1"/>
-    </row>
-    <row r="26" spans="2:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="5"/>
-      <c r="C26" s="8"/>
-      <c r="D26" s="4"/>
-      <c r="E26" s="5"/>
-      <c r="F26" s="6"/>
-      <c r="G26" s="1"/>
-    </row>
-    <row r="27" spans="2:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B27" s="5"/>
-      <c r="C27" s="8"/>
-      <c r="D27" s="4"/>
-      <c r="E27" s="5"/>
-      <c r="F27" s="6"/>
-      <c r="G27" s="1"/>
-    </row>
-    <row r="28" spans="2:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B28" s="5"/>
-      <c r="C28" s="8"/>
-      <c r="D28" s="4"/>
-      <c r="E28" s="5"/>
-      <c r="F28" s="6"/>
-      <c r="G28" s="1"/>
-    </row>
-    <row r="29" spans="2:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B29" s="5"/>
-      <c r="C29" s="8"/>
-      <c r="D29" s="4"/>
-      <c r="E29" s="5"/>
-      <c r="F29" s="6"/>
-      <c r="G29" s="1"/>
-    </row>
-    <row r="30" spans="2:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B30" s="5"/>
-      <c r="C30" s="8"/>
-      <c r="D30" s="4"/>
-      <c r="E30" s="5"/>
-      <c r="F30" s="6"/>
-      <c r="G30" s="1"/>
-    </row>
-    <row r="31" spans="2:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="F31" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G31" s="3">
-        <f>SUM(G6:G30)</f>
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="B3:G3"/>
-    <mergeCell ref="G4:G5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="B4:D4"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="78" orientation="landscape"/>
-</worksheet>
 </file>